--- a/templates/3_DieuChuyen.xlsx
+++ b/templates/3_DieuChuyen.xlsx
@@ -670,7 +670,11 @@
           <t>Số (Number)</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Số lượng sổ sách = tổng thiết bị cùng Mã tài sản + Đặc điểm + Nơi sử dụng</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
